--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T10:55:45+00:00</t>
+    <t>2023-04-05T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:18:36+00:00</t>
+    <t>2023-04-05T15:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1893,7 +1893,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/fr-address-extended}
+    <t xml:space="preserve">Address {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-address-extended}
 </t>
   </si>
   <si>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6699" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5631" uniqueCount="649">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1564,39 +1564,6 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
   </si>
   <si>
-    <t>Organization.type:activiteINSEE.id</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.extension</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.coding</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.coding.code</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.coding.display</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Organization.type:activiteINSEE.text</t>
-  </si>
-  <si>
     <t>Organization.type:statutJuridiqueINSEE</t>
   </si>
   <si>
@@ -1609,39 +1576,6 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
   </si>
   <si>
-    <t>Organization.type:statutJuridiqueINSEE.id</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.extension</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.coding</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.coding.code</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.coding.display</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Organization.type:statutJuridiqueINSEE.text</t>
-  </si>
-  <si>
     <t>Organization.type:CategorieEtablissement</t>
   </si>
   <si>
@@ -1658,39 +1592,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J162-ESPIC-RASS/FHIR/JDV-J162-ESPIC-RASS</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.id</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.extension</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.coding</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.coding.code</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.coding.display</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH.text</t>
   </si>
   <si>
     <t>Organization.name</t>
@@ -2421,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ207"/>
+  <dimension ref="A1:AJ174"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.27734375" customWidth="true" bestFit="true"/>
@@ -16666,9 +16567,11 @@
         <v>501</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="D140" t="s" s="2">
         <v>71</v>
       </c>
@@ -16677,7 +16580,7 @@
         <v>72</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>71</v>
@@ -16686,19 +16589,23 @@
         <v>71</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>93</v>
+        <v>258</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>94</v>
+        <v>392</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>71</v>
       </c>
@@ -16722,13 +16629,13 @@
         <v>71</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>71</v>
+        <v>503</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>71</v>
+        <v>504</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>71</v>
@@ -16746,31 +16653,33 @@
         <v>71</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>96</v>
+        <v>391</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C141" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="D141" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -16786,21 +16695,23 @@
         <v>71</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>99</v>
+        <v>258</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>100</v>
+        <v>392</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>101</v>
+        <v>393</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>71</v>
       </c>
@@ -16824,31 +16735,31 @@
         <v>71</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>71</v>
+        <v>396</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>71</v>
+        <v>397</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>106</v>
+        <v>391</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>72</v>
@@ -16860,17 +16771,19 @@
         <v>90</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="D142" t="s" s="2">
         <v>71</v>
       </c>
@@ -16891,19 +16804,19 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>132</v>
+        <v>258</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>71</v>
@@ -16928,13 +16841,13 @@
         <v>71</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>71</v>
+        <v>509</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>71</v>
+        <v>510</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>71</v>
@@ -16952,7 +16865,7 @@
         <v>71</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>72</v>
@@ -16969,10 +16882,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>416</v>
+        <v>511</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16992,19 +16905,23 @@
         <v>71</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>93</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>94</v>
+        <v>512</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>71</v>
       </c>
@@ -17052,7 +16969,7 @@
         <v>71</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>96</v>
+        <v>511</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>72</v>
@@ -17061,22 +16978,22 @@
         <v>78</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>71</v>
+        <v>339</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>418</v>
+        <v>516</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -17095,18 +17012,20 @@
         <v>71</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>100</v>
+        <v>517</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>101</v>
+        <v>518</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O144" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>71</v>
       </c>
@@ -17142,19 +17061,19 @@
         <v>71</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>106</v>
+        <v>516</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>72</v>
@@ -17166,15 +17085,15 @@
         <v>90</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>420</v>
+        <v>521</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17185,7 +17104,7 @@
         <v>72</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>71</v>
@@ -17194,22 +17113,22 @@
         <v>71</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>120</v>
+        <v>522</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>421</v>
+        <v>523</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>422</v>
+        <v>524</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>423</v>
+        <v>525</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>424</v>
+        <v>526</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>71</v>
@@ -17258,27 +17177,27 @@
         <v>71</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>426</v>
+        <v>521</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>90</v>
+        <v>527</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>91</v>
+        <v>528</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>507</v>
+        <v>529</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>428</v>
+        <v>529</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17298,20 +17217,18 @@
         <v>71</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>93</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>429</v>
+        <v>94</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>71</v>
@@ -17360,7 +17277,7 @@
         <v>71</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>432</v>
+        <v>96</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>72</v>
@@ -17369,29 +17286,29 @@
         <v>78</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>434</v>
+        <v>530</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>71</v>
@@ -17400,23 +17317,21 @@
         <v>71</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>435</v>
+        <v>100</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>436</v>
+        <v>101</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>71</v>
       </c>
@@ -17452,43 +17367,45 @@
         <v>71</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>439</v>
+        <v>106</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C148" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C148" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="D148" t="s" s="2">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -17504,23 +17421,21 @@
         <v>71</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>93</v>
+        <v>533</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>442</v>
+        <v>534</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>443</v>
+        <v>183</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>71</v>
       </c>
@@ -17568,27 +17483,27 @@
         <v>71</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>445</v>
+        <v>106</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>447</v>
+        <v>535</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17596,7 +17511,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>78</v>
@@ -17611,20 +17526,18 @@
         <v>79</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>293</v>
+        <v>154</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>448</v>
+        <v>536</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>449</v>
+        <v>537</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>71</v>
       </c>
@@ -17648,13 +17561,13 @@
         <v>71</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>71</v>
+        <v>539</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>71</v>
+        <v>540</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>71</v>
@@ -17672,7 +17585,7 @@
         <v>71</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>452</v>
+        <v>541</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>72</v>
@@ -17681,7 +17594,7 @@
         <v>78</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>90</v>
+        <v>542</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>91</v>
@@ -17689,10 +17602,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>454</v>
+        <v>543</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17700,7 +17613,7 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>78</v>
@@ -17718,16 +17631,16 @@
         <v>93</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>455</v>
+        <v>544</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>456</v>
+        <v>545</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>457</v>
+        <v>546</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>458</v>
+        <v>547</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>71</v>
@@ -17776,7 +17689,7 @@
         <v>71</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>459</v>
+        <v>548</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>72</v>
@@ -17793,14 +17706,12 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>71</v>
       </c>
@@ -17809,31 +17720,31 @@
         <v>72</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I151" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>258</v>
+        <v>154</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>392</v>
+        <v>550</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>393</v>
+        <v>551</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>394</v>
+        <v>552</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>395</v>
+        <v>553</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>71</v>
@@ -17861,10 +17772,10 @@
         <v>259</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>514</v>
+        <v>554</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>515</v>
+        <v>555</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>71</v>
@@ -17882,13 +17793,13 @@
         <v>71</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>391</v>
+        <v>556</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>90</v>
@@ -17899,10 +17810,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>405</v>
+        <v>557</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17922,18 +17833,20 @@
         <v>71</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>93</v>
+        <v>558</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>94</v>
+        <v>559</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>71</v>
@@ -17982,7 +17895,7 @@
         <v>71</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>96</v>
+        <v>562</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>72</v>
@@ -17991,29 +17904,29 @@
         <v>78</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>517</v>
+        <v>563</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>407</v>
+        <v>563</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>71</v>
@@ -18022,19 +17935,19 @@
         <v>71</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>100</v>
+        <v>564</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>101</v>
+        <v>565</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>102</v>
+        <v>566</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -18072,39 +17985,39 @@
         <v>71</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>106</v>
+        <v>567</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>107</v>
+        <v>377</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>518</v>
+        <v>568</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>409</v>
+        <v>568</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18115,7 +18028,7 @@
         <v>72</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>71</v>
@@ -18124,23 +18037,19 @@
         <v>71</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>410</v>
+        <v>94</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>71</v>
       </c>
@@ -18188,38 +18097,38 @@
         <v>71</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>414</v>
+        <v>96</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>519</v>
+        <v>569</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>416</v>
+        <v>569</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>71</v>
@@ -18231,15 +18140,17 @@
         <v>71</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N155" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>71</v>
@@ -18276,50 +18187,50 @@
         <v>71</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AC155" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AD155" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>71</v>
+        <v>107</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>418</v>
+        <v>570</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>71</v>
@@ -18328,19 +18239,19 @@
         <v>71</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>99</v>
+        <v>218</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>100</v>
+        <v>571</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -18378,39 +18289,39 @@
         <v>71</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>106</v>
+        <v>222</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>90</v>
+        <v>223</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>521</v>
+        <v>572</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>420</v>
+        <v>572</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18433,24 +18344,24 @@
         <v>79</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>120</v>
+        <v>218</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>421</v>
+        <v>573</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>422</v>
+        <v>227</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q157" s="2"/>
+      <c r="Q157" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="R157" t="s" s="2">
         <v>71</v>
       </c>
@@ -18494,7 +18405,7 @@
         <v>71</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>426</v>
+        <v>230</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>72</v>
@@ -18503,7 +18414,7 @@
         <v>78</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>90</v>
+        <v>223</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>91</v>
@@ -18511,10 +18422,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>522</v>
+        <v>574</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>428</v>
+        <v>574</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18525,7 +18436,7 @@
         <v>72</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>71</v>
@@ -18534,21 +18445,23 @@
         <v>71</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>93</v>
+        <v>575</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>429</v>
+        <v>576</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>430</v>
+        <v>577</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>71</v>
       </c>
@@ -18596,27 +18509,27 @@
         <v>71</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>432</v>
+        <v>574</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>91</v>
+        <v>580</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>523</v>
+        <v>581</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>434</v>
+        <v>581</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18639,19 +18552,19 @@
         <v>79</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>154</v>
+        <v>582</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>435</v>
+        <v>583</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>436</v>
+        <v>584</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>438</v>
+        <v>586</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>71</v>
@@ -18700,7 +18613,7 @@
         <v>71</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>439</v>
+        <v>581</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>72</v>
@@ -18712,15 +18625,15 @@
         <v>90</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>91</v>
+        <v>384</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>524</v>
+        <v>587</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>441</v>
+        <v>587</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18740,23 +18653,19 @@
         <v>71</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K160" t="s" s="2">
         <v>93</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>442</v>
+        <v>94</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="N160" s="2"/>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>71</v>
       </c>
@@ -18804,7 +18713,7 @@
         <v>71</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>445</v>
+        <v>96</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>72</v>
@@ -18813,29 +18722,29 @@
         <v>78</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>525</v>
+        <v>588</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>447</v>
+        <v>588</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>71</v>
@@ -18844,23 +18753,21 @@
         <v>71</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>293</v>
+        <v>99</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>448</v>
+        <v>100</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>449</v>
+        <v>101</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>71</v>
       </c>
@@ -18896,39 +18803,39 @@
         <v>71</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>452</v>
+        <v>106</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>526</v>
+        <v>589</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>454</v>
+        <v>589</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18954,17 +18861,15 @@
         <v>93</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>455</v>
+        <v>590</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>456</v>
+        <v>591</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>71</v>
       </c>
@@ -19012,7 +18917,7 @@
         <v>71</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>459</v>
+        <v>593</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>72</v>
@@ -19021,7 +18926,7 @@
         <v>78</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>90</v>
+        <v>594</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>91</v>
@@ -19029,14 +18934,12 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>527</v>
+        <v>595</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C163" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
         <v>71</v>
       </c>
@@ -19045,7 +18948,7 @@
         <v>72</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>71</v>
@@ -19057,20 +18960,18 @@
         <v>79</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>258</v>
+        <v>120</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>392</v>
+        <v>596</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>393</v>
+        <v>597</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>71</v>
       </c>
@@ -19094,13 +18995,13 @@
         <v>71</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>396</v>
+        <v>599</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>71</v>
@@ -19118,13 +19019,13 @@
         <v>71</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>391</v>
+        <v>600</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>90</v>
@@ -19135,14 +19036,12 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>529</v>
+        <v>601</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>71</v>
       </c>
@@ -19151,7 +19050,7 @@
         <v>72</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>71</v>
@@ -19163,20 +19062,18 @@
         <v>79</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>258</v>
+        <v>334</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>392</v>
+        <v>602</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>393</v>
+        <v>603</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
         <v>71</v>
       </c>
@@ -19200,13 +19097,13 @@
         <v>71</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>259</v>
+        <v>71</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>531</v>
+        <v>71</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>532</v>
+        <v>71</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>71</v>
@@ -19224,13 +19121,13 @@
         <v>71</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>391</v>
+        <v>605</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>90</v>
@@ -19241,10 +19138,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>533</v>
+        <v>606</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>405</v>
+        <v>606</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19264,18 +19161,20 @@
         <v>71</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K165" t="s" s="2">
         <v>93</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>94</v>
+        <v>607</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N165" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>71</v>
@@ -19324,7 +19223,7 @@
         <v>71</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>96</v>
+        <v>610</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>72</v>
@@ -19333,29 +19232,29 @@
         <v>78</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>534</v>
+        <v>611</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>407</v>
+        <v>611</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>71</v>
@@ -19367,18 +19266,20 @@
         <v>71</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>99</v>
+        <v>612</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>100</v>
+        <v>613</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>101</v>
+        <v>614</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O166" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="P166" t="s" s="2">
         <v>71</v>
       </c>
@@ -19414,19 +19315,19 @@
         <v>71</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>106</v>
+        <v>611</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>72</v>
@@ -19438,15 +19339,15 @@
         <v>90</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>535</v>
+        <v>617</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>409</v>
+        <v>617</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19457,7 +19358,7 @@
         <v>72</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>71</v>
@@ -19466,23 +19367,19 @@
         <v>71</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>410</v>
+        <v>94</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>71</v>
       </c>
@@ -19530,38 +19427,38 @@
         <v>71</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>414</v>
+        <v>96</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>536</v>
+        <v>618</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>416</v>
+        <v>618</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>71</v>
@@ -19573,15 +19470,17 @@
         <v>71</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N168" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>71</v>
@@ -19618,43 +19517,43 @@
         <v>71</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>71</v>
+        <v>107</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>537</v>
+        <v>619</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>418</v>
+        <v>619</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>98</v>
+        <v>620</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -19667,24 +19566,26 @@
         <v>71</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>100</v>
+        <v>621</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>101</v>
+        <v>622</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="O169" s="2"/>
+      <c r="O169" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>71</v>
       </c>
@@ -19720,19 +19621,19 @@
         <v>71</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>106</v>
+        <v>623</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>72</v>
@@ -19749,10 +19650,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>538</v>
+        <v>624</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>420</v>
+        <v>624</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19772,22 +19673,22 @@
         <v>71</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>421</v>
+        <v>625</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>422</v>
+        <v>626</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>423</v>
+        <v>627</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>424</v>
+        <v>628</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>71</v>
@@ -19812,13 +19713,13 @@
         <v>71</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>71</v>
+        <v>629</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>71</v>
+        <v>630</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>71</v>
@@ -19836,7 +19737,7 @@
         <v>71</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>426</v>
+        <v>624</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>72</v>
@@ -19853,10 +19754,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>539</v>
+        <v>631</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>428</v>
+        <v>631</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19876,21 +19777,23 @@
         <v>71</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>93</v>
+        <v>632</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>429</v>
+        <v>633</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>430</v>
+        <v>634</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O171" s="2"/>
+        <v>635</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="P171" t="s" s="2">
         <v>71</v>
       </c>
@@ -19938,7 +19841,7 @@
         <v>71</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>432</v>
+        <v>631</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>72</v>
@@ -19955,10 +19858,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>540</v>
+        <v>637</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>434</v>
+        <v>637</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19969,7 +19872,7 @@
         <v>72</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>71</v>
@@ -19978,22 +19881,20 @@
         <v>71</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>154</v>
+        <v>522</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>435</v>
+        <v>523</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>438</v>
+        <v>638</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>71</v>
@@ -20042,27 +19943,27 @@
         <v>71</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>439</v>
+        <v>637</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>91</v>
+        <v>639</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>541</v>
+        <v>640</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>441</v>
+        <v>640</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20082,22 +19983,22 @@
         <v>71</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>93</v>
+        <v>641</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>442</v>
+        <v>576</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>443</v>
+        <v>577</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>437</v>
+        <v>578</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>444</v>
+        <v>642</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>71</v>
@@ -20146,7 +20047,7 @@
         <v>71</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>445</v>
+        <v>640</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>72</v>
@@ -20163,10 +20064,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>542</v>
+        <v>643</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>447</v>
+        <v>643</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20177,7 +20078,7 @@
         <v>72</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>71</v>
@@ -20186,22 +20087,22 @@
         <v>71</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>293</v>
+        <v>644</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>448</v>
+        <v>645</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>449</v>
+        <v>646</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>450</v>
+        <v>647</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>451</v>
+        <v>648</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>71</v>
@@ -20250,3408 +20151,18 @@
         <v>71</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>452</v>
+        <v>643</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C175" s="2"/>
-      <c r="D175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E175" s="2"/>
-      <c r="F175" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G175" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K175" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L175" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="P175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q175" s="2"/>
-      <c r="R175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE175" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF175" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG175" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH175" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI175" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ175" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E176" s="2"/>
-      <c r="F176" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G176" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J176" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K176" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="P176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q176" s="2"/>
-      <c r="R176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AG176" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH176" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI176" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AJ176" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C177" s="2"/>
-      <c r="D177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E177" s="2"/>
-      <c r="F177" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K177" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L177" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="P177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q177" s="2"/>
-      <c r="R177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AG177" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI177" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ177" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C178" s="2"/>
-      <c r="D178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E178" s="2"/>
-      <c r="F178" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K178" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="P178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q178" s="2"/>
-      <c r="R178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AG178" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI178" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AJ178" t="s" s="2">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E179" s="2"/>
-      <c r="F179" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K179" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" s="2"/>
-      <c r="P179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q179" s="2"/>
-      <c r="R179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AG179" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI179" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AJ179" t="s" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C180" s="2"/>
-      <c r="D180" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="E180" s="2"/>
-      <c r="F180" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O180" s="2"/>
-      <c r="P180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q180" s="2"/>
-      <c r="R180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG180" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI180" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ180" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="D181" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G181" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K181" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O181" s="2"/>
-      <c r="P181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q181" s="2"/>
-      <c r="R181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG181" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI181" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ181" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J182" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K182" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="L182" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O182" s="2"/>
-      <c r="P182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q182" s="2"/>
-      <c r="R182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X182" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="Z182" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AA182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE182" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF182" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AG182" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI182" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AJ182" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C183" s="2"/>
-      <c r="D183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E183" s="2"/>
-      <c r="F183" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G183" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J183" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K183" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L183" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="P183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q183" s="2"/>
-      <c r="R183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE183" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF183" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG183" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH183" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI183" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ183" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C184" s="2"/>
-      <c r="D184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E184" s="2"/>
-      <c r="F184" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I184" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J184" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K184" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="L184" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="P184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q184" s="2"/>
-      <c r="R184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X184" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y184" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ184" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C185" s="2"/>
-      <c r="D185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G185" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K185" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="L185" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O185" s="2"/>
-      <c r="P185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q185" s="2"/>
-      <c r="R185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ185" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O186" s="2"/>
-      <c r="P186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N187" s="2"/>
-      <c r="O187" s="2"/>
-      <c r="P187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O188" s="2"/>
-      <c r="P188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O189" s="2"/>
-      <c r="P189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O190" s="2"/>
-      <c r="P190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q190" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="R190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="P192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N193" s="2"/>
-      <c r="O193" s="2"/>
-      <c r="P193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C194" s="2"/>
-      <c r="D194" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G194" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K194" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O194" s="2"/>
-      <c r="P194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AF194" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O195" s="2"/>
-      <c r="P195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G196" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K196" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="O196" s="2"/>
-      <c r="P196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q196" s="2"/>
-      <c r="R196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X196" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="Y196" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="Z196" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AA196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE196" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF196" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AG196" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH196" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI196" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ196" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C197" s="2"/>
-      <c r="D197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E197" s="2"/>
-      <c r="F197" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G197" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J197" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K197" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="L197" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O197" s="2"/>
-      <c r="P197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q197" s="2"/>
-      <c r="R197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE197" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF197" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AG197" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH197" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI197" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ197" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="C198" s="2"/>
-      <c r="D198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E198" s="2"/>
-      <c r="F198" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G198" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J198" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K198" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L198" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O198" s="2"/>
-      <c r="P198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q198" s="2"/>
-      <c r="R198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE198" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF198" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AG198" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH198" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI198" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ198" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C199" s="2"/>
-      <c r="D199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E199" s="2"/>
-      <c r="F199" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G199" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K199" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="L199" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O199" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="P199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q199" s="2"/>
-      <c r="R199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF199" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AG199" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH199" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI199" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ199" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C200" s="2"/>
-      <c r="D200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E200" s="2"/>
-      <c r="F200" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G200" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K200" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L200" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N200" s="2"/>
-      <c r="O200" s="2"/>
-      <c r="P200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q200" s="2"/>
-      <c r="R200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF200" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AG200" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH200" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI200" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AJ200" t="s" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="C201" s="2"/>
-      <c r="D201" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="E201" s="2"/>
-      <c r="F201" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G201" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K201" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L201" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M201" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O201" s="2"/>
-      <c r="P201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q201" s="2"/>
-      <c r="R201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB201" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AC201" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AD201" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE201" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AF201" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG201" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH201" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI201" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ201" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C202" s="2"/>
-      <c r="D202" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="E202" s="2"/>
-      <c r="F202" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G202" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I202" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J202" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K202" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L202" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="P202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q202" s="2"/>
-      <c r="R202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE202" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF202" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AG202" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH202" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI202" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ202" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="C203" s="2"/>
-      <c r="D203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E203" s="2"/>
-      <c r="F203" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G203" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K203" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="L203" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="M203" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="P203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q203" s="2"/>
-      <c r="R203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X203" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="Y203" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="Z203" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="AA203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE203" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF203" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AG203" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH203" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI203" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ203" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="C204" s="2"/>
-      <c r="D204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E204" s="2"/>
-      <c r="F204" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G204" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K204" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="L204" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="M204" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="P204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q204" s="2"/>
-      <c r="R204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE204" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF204" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AG204" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH204" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI204" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ204" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C205" s="2"/>
-      <c r="D205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E205" s="2"/>
-      <c r="F205" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G205" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K205" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="L205" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="M205" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N205" s="2"/>
-      <c r="O205" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="P205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q205" s="2"/>
-      <c r="R205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE205" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF205" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AG205" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH205" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI205" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ205" t="s" s="2">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="B206" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="C206" s="2"/>
-      <c r="D206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E206" s="2"/>
-      <c r="F206" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G206" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K206" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="L206" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M206" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="P206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q206" s="2"/>
-      <c r="R206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE206" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF206" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="AG206" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH206" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI206" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ206" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="C207" s="2"/>
-      <c r="D207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E207" s="2"/>
-      <c r="F207" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G207" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K207" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="L207" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="M207" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="O207" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="P207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q207" s="2"/>
-      <c r="R207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE207" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF207" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AG207" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH207" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI207" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ207" t="s" s="2">
         <v>384</v>
       </c>
     </row>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:24:37+00:00</t>
+    <t>2023-04-05T17:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-07T12:42:40+00:00</t>
+    <t>2023-04-12T10:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:08:35+00:00</t>
+    <t>2023-04-12T14:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T14:03:54+00:00</t>
+    <t>2023-04-13T07:49:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$165</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5520" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5321" uniqueCount="644">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,49 +738,55 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>Organization.extension:digitalCertificate</t>
-  </si>
-  <si>
-    <t>digitalCertificate</t>
+    <t>Organization.extension:organization-digitalCertificate</t>
+  </si>
+  <si>
+    <t>organization-digitalCertificate</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/digitalCertificate}
 </t>
   </si>
   <si>
-    <t>Organization.extension:pharmacyLicence</t>
-  </si>
-  <si>
-    <t>pharmacyLicence</t>
+    <t>[DR] : certificat</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-pharmacyLicence</t>
+  </si>
+  <si>
+    <t>organization-pharmacyLicence</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/organization-pharmacyLicence}
 </t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS</t>
-  </si>
-  <si>
-    <t>mailboxMSS</t>
+    <t>numeroLicence</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS</t>
+  </si>
+  <si>
+    <t>organization-mailboxMSS</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-mailbox-mss}
 </t>
   </si>
   <si>
-    <t>AS Mailbox MSS Extension</t>
+    <t>boiteLettresMSS</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'annuaire santé pour décrire les boîtes aux lettres du service de messagerie sécurisée de santé (MSSanté) rattachées aux professionnels et aux structures.</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:value</t>
+    <t>Organization.extension:organization-mailboxMSS.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:value</t>
   </si>
   <si>
     <t>value</t>
@@ -792,13 +798,13 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:value.id</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:value.id</t>
   </si>
   <si>
     <t>Organization.extension.extension.id</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:value.extension</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:value.extension</t>
   </si>
   <si>
     <t>Organization.extension.extension.extension</t>
@@ -807,41 +813,41 @@
     <t>Extension</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:value.url</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:value.url</t>
   </si>
   <si>
     <t>Organization.extension.extension.url</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:value.value[x]</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:value.value[x]</t>
   </si>
   <si>
     <t>Organization.extension.extension.value[x]</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:type</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:type</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:type.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:type.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:type.value[x]</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:type.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:type.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:type.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:type.value[x]:valueCodeableConcept</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:type.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>valueCodeableConcept</t>
@@ -862,64 +868,67 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:description</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:description.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:description.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:description.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:description.value[x]</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:description</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:description.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:description.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:description.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:description.value[x]</t>
   </si>
   <si>
     <t>Description fonctionnelle de la boîte aux lettres</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:responsible</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:responsible</t>
   </si>
   <si>
     <t>responsible</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:responsible.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:responsible.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:responsible.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:responsible.value[x]</t>
+    <t>[DR] : mailBoxMSS.responsable</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:responsible.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:responsible.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:responsible.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:responsible.value[x]</t>
   </si>
   <si>
     <t>Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:service</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:service</t>
   </si>
   <si>
     <t>service</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:service.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:service.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:service.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:service.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:service.value[x]:valueString</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:service.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:service.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:service.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:service.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:service.value[x]:valueString</t>
   </si>
   <si>
     <t>valueString</t>
@@ -928,53 +937,56 @@
     <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:phone</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:phone</t>
   </si>
   <si>
     <t>phone</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:phone.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:phone.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:phone.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:phone.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:phone.value[x]:valueString</t>
+    <t>[DR] : mailBoxMSS.phone</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:phone.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:phone.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:phone.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:phone.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:phone.value[x]:valueString</t>
   </si>
   <si>
     <t>Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:digitization</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:digitization</t>
   </si>
   <si>
     <t>digitization</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:digitization.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:digitization.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:digitization.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:digitization.value[x]</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:digitization.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:digitization.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:digitization.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:digitization.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:digitization.value[x]:valueBoolean</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:digitization.value[x]:valueBoolean</t>
   </si>
   <si>
     <t>valueBoolean</t>
@@ -987,25 +999,25 @@
 - N : Dématérialisation refusée</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:publication</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:publication</t>
   </si>
   <si>
     <t>publication</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:publication.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:publication.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:publication.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:publication.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:publication.value[x]:valueBoolean</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:publication.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:publication.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:publication.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:publication.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:publication.value[x]:valueBoolean</t>
   </si>
   <si>
     <t>ndicateur liste rouge</t>
@@ -1015,31 +1027,31 @@
 N: La boîte aux lettres peut être publiée</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:date</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:date</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.extension:date.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:date.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:date.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.extension:date.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.extension:mailboxMSS.url</t>
+    <t>Organization.extension:organization-mailboxMSS.extension:date.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:date.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:date.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.extension:date.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.extension:organization-mailboxMSS.url</t>
   </si>
   <si>
     <t>http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-mailbox-mss</t>
   </si>
   <si>
-    <t>Organization.extension:mailboxMSS.value[x]</t>
+    <t>Organization.extension:organization-mailboxMSS.value[x]</t>
   </si>
   <si>
     <t>base64Binary
@@ -1276,7 +1288,7 @@
     <t>organizationType</t>
   </si>
   <si>
-    <t>Type de strcuture</t>
+    <t>typeEtablissement</t>
   </si>
   <si>
     <t>Entitité Juridique : LEGAL-ENTITY; 
@@ -1460,7 +1472,7 @@
     <t>secteurActiviteRASS</t>
   </si>
   <si>
-    <t>Un secteur d'activité regroupe les établissements partageant la même activité de santé.</t>
+    <t>Un secteur d'activité regroupe les établissements partageant la même activité de santé</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J101-SecteurActivite-RASS/FHIR/JDV-J101-SecteurActivite-RASS</t>
@@ -1554,12 +1566,6 @@
   </si>
   <si>
     <t>Organization.type:categorieEtablissementRASS.text</t>
-  </si>
-  <si>
-    <t>Organization.type:organizationActivityField</t>
-  </si>
-  <si>
-    <t>organizationActivityField</t>
   </si>
   <si>
     <t>Organization.type:activiteINSEE</t>
@@ -1572,9 +1578,6 @@
 Plus précisément, on distingue le code APET pour les EG.</t>
   </si>
   <si>
-    <t>Sous-classes de la Nomenclature d'Activités Française - INSEE</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
   </si>
   <si>
@@ -1590,16 +1593,10 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
   </si>
   <si>
-    <t>Organization.type:CategorieEtablissement</t>
-  </si>
-  <si>
-    <t>CategorieEtablissement</t>
-  </si>
-  <si>
-    <t>Organization.type:SPH</t>
-  </si>
-  <si>
-    <t>SPH</t>
+    <t>Organization.type:sphParticipation</t>
+  </si>
+  <si>
+    <t>sphParticipation</t>
   </si>
   <si>
     <t>Modalités de participation au service public hospitalier</t>
@@ -1662,6 +1659,10 @@
 org-3</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+  </si>
+  <si>
     <t>Organization.telecom.id</t>
   </si>
   <si>
@@ -1783,24 +1784,6 @@
     <t>ContactPoint.period</t>
   </si>
   <si>
-    <t>Organization.telecom.period.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom.period.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom.period.start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>Organization.telecom.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
     <t>Organization.address</t>
   </si>
   <si>
@@ -1827,7 +1810,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
@@ -2347,12 +2330,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ171"/>
+  <dimension ref="A1:AJ165"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="78.37109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="90.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.453125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="29.30859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5378,7 +5361,7 @@
         <v>233</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>183</v>
@@ -5449,13 +5432,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>176</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>71</v>
@@ -5468,7 +5451,7 @@
         <v>73</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>71</v>
@@ -5477,10 +5460,10 @@
         <v>71</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>183</v>
@@ -5551,13 +5534,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>176</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>71</v>
@@ -5570,7 +5553,7 @@
         <v>73</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>71</v>
@@ -5579,13 +5562,13 @@
         <v>71</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5648,12 +5631,12 @@
         <v>90</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>71</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>192</v>
@@ -5753,7 +5736,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>194</v>
@@ -5855,13 +5838,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>71</v>
@@ -5886,10 +5869,10 @@
         <v>99</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5957,10 +5940,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6057,10 +6040,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6086,10 +6069,10 @@
         <v>99</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6157,10 +6140,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6200,7 +6183,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>71</v>
@@ -6259,10 +6242,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6359,13 +6342,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>71</v>
@@ -6390,10 +6373,10 @@
         <v>99</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6461,10 +6444,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6561,10 +6544,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6590,10 +6573,10 @@
         <v>99</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6661,10 +6644,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6704,7 +6687,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>71</v>
@@ -6763,10 +6746,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6789,7 +6772,7 @@
         <v>71</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>205</v>
@@ -6861,13 +6844,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>71</v>
@@ -6889,13 +6872,13 @@
         <v>71</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>205</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6922,13 +6905,13 @@
         <v>71</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>71</v>
@@ -6963,7 +6946,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>194</v>
@@ -6994,10 +6977,10 @@
         <v>99</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7065,10 +7048,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7165,10 +7148,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7194,10 +7177,10 @@
         <v>99</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7265,10 +7248,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7367,10 +7350,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7396,7 +7379,7 @@
         <v>93</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>206</v>
@@ -7467,13 +7450,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>71</v>
@@ -7498,10 +7481,10 @@
         <v>99</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7569,10 +7552,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7669,10 +7652,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7698,10 +7681,10 @@
         <v>99</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7769,10 +7752,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7812,7 +7795,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>71</v>
@@ -7871,10 +7854,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7900,7 +7883,7 @@
         <v>93</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>206</v>
@@ -7971,13 +7954,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>71</v>
@@ -8002,10 +7985,10 @@
         <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8073,10 +8056,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8173,10 +8156,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8202,10 +8185,10 @@
         <v>99</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8273,10 +8256,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8316,7 +8299,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>71</v>
@@ -8375,10 +8358,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8473,13 +8456,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>71</v>
@@ -8504,7 +8487,7 @@
         <v>93</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>206</v>
@@ -8575,13 +8558,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>71</v>
@@ -8606,10 +8589,10 @@
         <v>99</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8677,10 +8660,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8777,10 +8760,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8806,10 +8789,10 @@
         <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8877,10 +8860,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8920,7 +8903,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>71</v>
@@ -8979,10 +8962,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9077,13 +9060,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>71</v>
@@ -9108,7 +9091,7 @@
         <v>93</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>206</v>
@@ -9179,13 +9162,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>71</v>
@@ -9210,10 +9193,10 @@
         <v>99</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9281,10 +9264,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9381,10 +9364,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9410,10 +9393,10 @@
         <v>99</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9481,10 +9464,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9524,7 +9507,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>71</v>
@@ -9583,10 +9566,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9609,7 +9592,7 @@
         <v>71</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>205</v>
@@ -9681,13 +9664,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>71</v>
@@ -9709,16 +9692,16 @@
         <v>71</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>206</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9785,13 +9768,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>71</v>
@@ -9816,10 +9799,10 @@
         <v>99</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9887,10 +9870,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9987,10 +9970,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10016,10 +9999,10 @@
         <v>99</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10087,10 +10070,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10130,7 +10113,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>71</v>
@@ -10189,10 +10172,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10215,7 +10198,7 @@
         <v>71</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>205</v>
@@ -10287,13 +10270,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>71</v>
@@ -10315,16 +10298,16 @@
         <v>71</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="M79" t="s" s="2">
         <v>206</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10391,13 +10374,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>71</v>
@@ -10407,10 +10390,10 @@
         <v>72</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>71</v>
@@ -10422,10 +10405,10 @@
         <v>99</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10493,10 +10476,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10593,10 +10576,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10622,10 +10605,10 @@
         <v>99</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10693,10 +10676,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10736,7 +10719,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>71</v>
@@ -10795,10 +10778,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10895,7 +10878,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>196</v>
@@ -10938,7 +10921,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>71</v>
@@ -10997,7 +10980,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>203</v>
@@ -11023,7 +11006,7 @@
         <v>71</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>205</v>
@@ -11097,10 +11080,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11126,16 +11109,16 @@
         <v>99</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>102</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>71</v>
@@ -11184,7 +11167,7 @@
         <v>105</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>72</v>
@@ -11201,10 +11184,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11218,7 +11201,7 @@
         <v>73</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>71</v>
@@ -11227,19 +11210,19 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>71</v>
@@ -11288,7 +11271,7 @@
         <v>71</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>72</v>
@@ -11297,18 +11280,18 @@
         <v>73</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11405,10 +11388,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11507,10 +11490,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11536,23 +11519,23 @@
         <v>154</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>71</v>
@@ -11570,13 +11553,13 @@
         <v>71</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>71</v>
@@ -11594,7 +11577,7 @@
         <v>71</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>72</v>
@@ -11611,10 +11594,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11637,19 +11620,19 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>71</v>
@@ -11677,10 +11660,10 @@
         <v>136</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>71</v>
@@ -11698,7 +11681,7 @@
         <v>71</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>72</v>
@@ -11715,10 +11698,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11744,16 +11727,16 @@
         <v>120</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>71</v>
@@ -11766,7 +11749,7 @@
         <v>71</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>71</v>
@@ -11802,7 +11785,7 @@
         <v>71</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>72</v>
@@ -11819,10 +11802,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11848,13 +11831,13 @@
         <v>93</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11868,7 +11851,7 @@
         <v>71</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>71</v>
@@ -11904,7 +11887,7 @@
         <v>71</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>72</v>
@@ -11921,10 +11904,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11938,7 +11921,7 @@
         <v>78</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>71</v>
@@ -11950,13 +11933,13 @@
         <v>204</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12006,7 +11989,7 @@
         <v>71</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>72</v>
@@ -12018,15 +12001,15 @@
         <v>90</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12040,7 +12023,7 @@
         <v>78</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>71</v>
@@ -12049,16 +12032,16 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12108,7 +12091,7 @@
         <v>71</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>72</v>
@@ -12120,15 +12103,15 @@
         <v>90</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12151,70 +12134,70 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="O97" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q97" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="R97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q97" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="R97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>72</v>
@@ -12231,10 +12214,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12248,7 +12231,7 @@
         <v>73</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>71</v>
@@ -12257,19 +12240,19 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>71</v>
@@ -12297,16 +12280,16 @@
         <v>144</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
@@ -12316,7 +12299,7 @@
         <v>105</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>72</v>
@@ -12333,13 +12316,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>71</v>
@@ -12361,19 +12344,19 @@
         <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>71</v>
@@ -12398,13 +12381,13 @@
         <v>71</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>71</v>
@@ -12422,7 +12405,7 @@
         <v>71</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>72</v>
@@ -12439,10 +12422,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12539,10 +12522,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12641,10 +12624,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12670,16 +12653,16 @@
         <v>132</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>71</v>
@@ -12728,7 +12711,7 @@
         <v>71</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>72</v>
@@ -12745,10 +12728,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12845,10 +12828,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12947,10 +12930,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12976,29 +12959,29 @@
         <v>120</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>71</v>
@@ -13034,7 +13017,7 @@
         <v>71</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>72</v>
@@ -13051,10 +13034,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13080,13 +13063,13 @@
         <v>93</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13136,7 +13119,7 @@
         <v>71</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>72</v>
@@ -13153,10 +13136,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13182,16 +13165,16 @@
         <v>154</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>71</v>
@@ -13240,7 +13223,7 @@
         <v>71</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>72</v>
@@ -13257,10 +13240,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13286,16 +13269,16 @@
         <v>93</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>71</v>
@@ -13344,7 +13327,7 @@
         <v>71</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>72</v>
@@ -13361,10 +13344,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13387,19 +13370,19 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>71</v>
@@ -13448,7 +13431,7 @@
         <v>71</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>72</v>
@@ -13465,10 +13448,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13494,16 +13477,16 @@
         <v>93</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>71</v>
@@ -13552,7 +13535,7 @@
         <v>71</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>72</v>
@@ -13569,13 +13552,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>71</v>
@@ -13597,19 +13580,19 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>71</v>
@@ -13634,13 +13617,13 @@
         <v>71</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>71</v>
@@ -13658,7 +13641,7 @@
         <v>71</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>72</v>
@@ -13675,10 +13658,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13775,10 +13758,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13877,10 +13860,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13906,16 +13889,16 @@
         <v>132</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>71</v>
@@ -13964,7 +13947,7 @@
         <v>71</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>72</v>
@@ -13981,10 +13964,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14081,10 +14064,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14183,10 +14166,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14212,29 +14195,29 @@
         <v>120</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T117" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="U117" t="s" s="2">
         <v>71</v>
@@ -14270,7 +14253,7 @@
         <v>71</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>72</v>
@@ -14287,10 +14270,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14316,13 +14299,13 @@
         <v>93</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -14372,7 +14355,7 @@
         <v>71</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>72</v>
@@ -14389,10 +14372,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14418,16 +14401,16 @@
         <v>154</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>71</v>
@@ -14476,7 +14459,7 @@
         <v>71</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>72</v>
@@ -14493,10 +14476,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14522,16 +14505,16 @@
         <v>93</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>71</v>
@@ -14580,7 +14563,7 @@
         <v>71</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>72</v>
@@ -14597,10 +14580,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14623,19 +14606,19 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>71</v>
@@ -14684,7 +14667,7 @@
         <v>71</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>72</v>
@@ -14701,10 +14684,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14730,16 +14713,16 @@
         <v>93</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>71</v>
@@ -14788,7 +14771,7 @@
         <v>71</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>72</v>
@@ -14805,13 +14788,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>71</v>
@@ -14833,19 +14816,19 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>71</v>
@@ -14870,13 +14853,13 @@
         <v>71</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>71</v>
@@ -14894,7 +14877,7 @@
         <v>71</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>72</v>
@@ -14911,10 +14894,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15011,10 +14994,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15113,10 +15096,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15142,16 +15125,16 @@
         <v>132</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>71</v>
@@ -15200,7 +15183,7 @@
         <v>71</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>72</v>
@@ -15217,10 +15200,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15317,10 +15300,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15419,10 +15402,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15448,23 +15431,23 @@
         <v>120</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>71</v>
@@ -15506,7 +15489,7 @@
         <v>71</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>72</v>
@@ -15523,10 +15506,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15552,13 +15535,13 @@
         <v>93</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -15608,7 +15591,7 @@
         <v>71</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>72</v>
@@ -15625,10 +15608,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15654,16 +15637,16 @@
         <v>154</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>71</v>
@@ -15712,7 +15695,7 @@
         <v>71</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>72</v>
@@ -15729,10 +15712,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15758,16 +15741,16 @@
         <v>93</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>71</v>
@@ -15816,7 +15799,7 @@
         <v>71</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>72</v>
@@ -15833,10 +15816,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15859,19 +15842,19 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>71</v>
@@ -15920,7 +15903,7 @@
         <v>71</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>72</v>
@@ -15937,10 +15920,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15966,16 +15949,16 @@
         <v>93</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>71</v>
@@ -16024,7 +16007,7 @@
         <v>71</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>72</v>
@@ -16041,13 +16024,13 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>71</v>
@@ -16069,19 +16052,19 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>394</v>
+        <v>502</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>71</v>
@@ -16106,13 +16089,11 @@
         <v>71</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>399</v>
+        <v>503</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>71</v>
@@ -16130,7 +16111,7 @@
         <v>71</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>72</v>
@@ -16147,13 +16128,13 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>71</v>
@@ -16175,19 +16156,19 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>394</v>
+        <v>506</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>71</v>
@@ -16212,13 +16193,11 @@
         <v>71</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>71</v>
@@ -16236,7 +16215,7 @@
         <v>71</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>72</v>
@@ -16253,13 +16232,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>71</v>
@@ -16281,19 +16260,19 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>394</v>
+        <v>510</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>71</v>
@@ -16318,13 +16297,11 @@
         <v>71</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>71</v>
@@ -16342,7 +16319,7 @@
         <v>71</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>72</v>
@@ -16359,14 +16336,12 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>71</v>
       </c>
@@ -16375,10 +16350,10 @@
         <v>72</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>71</v>
@@ -16387,19 +16362,19 @@
         <v>79</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>263</v>
+        <v>93</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>394</v>
+        <v>513</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>395</v>
+        <v>514</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>396</v>
+        <v>515</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>397</v>
+        <v>516</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>71</v>
@@ -16424,13 +16399,13 @@
         <v>71</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>398</v>
+        <v>71</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>399</v>
+        <v>71</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>71</v>
@@ -16448,16 +16423,16 @@
         <v>71</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>393</v>
+        <v>512</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>90</v>
+        <v>345</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>91</v>
@@ -16465,14 +16440,12 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>71</v>
       </c>
@@ -16484,28 +16457,28 @@
         <v>73</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>263</v>
+        <v>93</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>394</v>
+        <v>518</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>395</v>
+        <v>519</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>396</v>
+        <v>520</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>397</v>
+        <v>521</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>71</v>
@@ -16530,13 +16503,13 @@
         <v>71</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>267</v>
+        <v>71</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>511</v>
+        <v>71</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>512</v>
+        <v>71</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>71</v>
@@ -16554,7 +16527,7 @@
         <v>71</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>393</v>
+        <v>517</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>72</v>
@@ -16571,10 +16544,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16585,31 +16558,31 @@
         <v>72</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>93</v>
+        <v>523</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>71</v>
@@ -16658,27 +16631,27 @@
         <v>71</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>341</v>
+        <v>528</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>91</v>
+        <v>529</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16689,7 +16662,7 @@
         <v>72</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>71</v>
@@ -16704,17 +16677,13 @@
         <v>93</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>519</v>
+        <v>94</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>71</v>
       </c>
@@ -16762,31 +16731,31 @@
         <v>71</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>518</v>
+        <v>96</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -16805,20 +16774,18 @@
         <v>71</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>524</v>
+        <v>99</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>525</v>
+        <v>100</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>526</v>
+        <v>101</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>71</v>
       </c>
@@ -16854,19 +16821,19 @@
         <v>71</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>523</v>
+        <v>106</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>72</v>
@@ -16875,22 +16842,24 @@
         <v>73</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>529</v>
+        <v>90</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>71</v>
+        <v>107</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C143" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="D143" t="s" s="2">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -16909,15 +16878,17 @@
         <v>71</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>93</v>
+        <v>534</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>94</v>
+        <v>535</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>71</v>
@@ -16966,38 +16937,38 @@
         <v>71</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>71</v>
+        <v>107</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>71</v>
@@ -17006,19 +16977,19 @@
         <v>71</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>100</v>
+        <v>537</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>101</v>
+        <v>538</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>102</v>
+        <v>539</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -17044,61 +17015,59 @@
         <v>71</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>71</v>
+        <v>269</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>71</v>
+        <v>540</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>71</v>
+        <v>541</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>106</v>
+        <v>542</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>90</v>
+        <v>543</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>78</v>
@@ -17110,21 +17079,23 @@
         <v>71</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>534</v>
+        <v>93</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>183</v>
+        <v>546</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>71</v>
       </c>
@@ -17172,27 +17143,27 @@
         <v>71</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>106</v>
+        <v>549</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17200,7 +17171,7 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>78</v>
@@ -17209,7 +17180,7 @@
         <v>71</v>
       </c>
       <c r="I146" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J146" t="s" s="2">
         <v>79</v>
@@ -17218,15 +17189,17 @@
         <v>154</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>71</v>
       </c>
@@ -17250,13 +17223,13 @@
         <v>71</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>71</v>
@@ -17274,7 +17247,7 @@
         <v>71</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>72</v>
@@ -17283,7 +17256,7 @@
         <v>78</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>543</v>
+        <v>90</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>91</v>
@@ -17291,10 +17264,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17302,7 +17275,7 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>78</v>
@@ -17317,20 +17290,18 @@
         <v>79</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>93</v>
+        <v>559</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>71</v>
       </c>
@@ -17378,7 +17349,7 @@
         <v>71</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>72</v>
@@ -17395,10 +17366,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17415,26 +17386,24 @@
         <v>71</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J148" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>71</v>
       </c>
@@ -17458,13 +17427,13 @@
         <v>71</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>267</v>
+        <v>71</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>555</v>
+        <v>71</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>556</v>
+        <v>71</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>71</v>
@@ -17482,7 +17451,7 @@
         <v>71</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>72</v>
@@ -17494,15 +17463,15 @@
         <v>90</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>91</v>
+        <v>383</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17513,7 +17482,7 @@
         <v>72</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>71</v>
@@ -17522,21 +17491,23 @@
         <v>71</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O149" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>71</v>
       </c>
@@ -17584,27 +17555,27 @@
         <v>71</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>91</v>
+        <v>575</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17627,18 +17598,20 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>204</v>
+        <v>577</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O150" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>71</v>
       </c>
@@ -17686,7 +17659,7 @@
         <v>71</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>72</v>
@@ -17698,15 +17671,15 @@
         <v>90</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>71</v>
+        <v>390</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17720,7 +17693,7 @@
         <v>78</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>71</v>
@@ -17803,10 +17776,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17905,10 +17878,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17922,7 +17895,7 @@
         <v>78</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>71</v>
@@ -17931,16 +17904,16 @@
         <v>79</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>218</v>
+        <v>93</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>220</v>
+        <v>586</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>221</v>
+        <v>587</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -17990,7 +17963,7 @@
         <v>71</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>222</v>
+        <v>588</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>72</v>
@@ -17999,7 +17972,7 @@
         <v>78</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>223</v>
+        <v>589</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>91</v>
@@ -18007,10 +17980,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18033,24 +18006,22 @@
         <v>79</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>227</v>
+        <v>592</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>228</v>
+        <v>593</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q154" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
         <v>71</v>
       </c>
@@ -18070,13 +18041,13 @@
         <v>71</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>71</v>
+        <v>594</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>71</v>
@@ -18094,7 +18065,7 @@
         <v>71</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>230</v>
+        <v>595</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>72</v>
@@ -18103,7 +18074,7 @@
         <v>78</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>223</v>
+        <v>90</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>91</v>
@@ -18111,10 +18082,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18125,7 +18096,7 @@
         <v>72</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>71</v>
@@ -18134,23 +18105,21 @@
         <v>71</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>576</v>
+        <v>340</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>71</v>
       </c>
@@ -18198,27 +18167,27 @@
         <v>71</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>581</v>
+        <v>91</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18241,20 +18210,18 @@
         <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>583</v>
+        <v>93</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>71</v>
       </c>
@@ -18302,7 +18269,7 @@
         <v>71</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>72</v>
@@ -18314,15 +18281,15 @@
         <v>90</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>386</v>
+        <v>91</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18333,10 +18300,10 @@
         <v>72</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>71</v>
@@ -18345,16 +18312,20 @@
         <v>71</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>93</v>
+        <v>607</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>94</v>
+        <v>608</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N157" s="2"/>
-      <c r="O157" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="P157" t="s" s="2">
         <v>71</v>
       </c>
@@ -18402,38 +18373,38 @@
         <v>71</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>96</v>
+        <v>606</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>71</v>
@@ -18445,17 +18416,15 @@
         <v>71</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>102</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>71</v>
@@ -18492,50 +18461,50 @@
         <v>71</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>71</v>
@@ -18544,19 +18513,19 @@
         <v>71</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>591</v>
+        <v>100</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>592</v>
+        <v>101</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>593</v>
+        <v>102</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -18594,73 +18563,75 @@
         <v>71</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>594</v>
+        <v>106</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>595</v>
+        <v>90</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>71</v>
+        <v>615</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I160" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J160" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O160" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>71</v>
       </c>
@@ -18684,13 +18655,13 @@
         <v>71</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>600</v>
+        <v>71</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>405</v>
+        <v>71</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>71</v>
@@ -18708,27 +18679,27 @@
         <v>71</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>601</v>
+        <v>618</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18748,21 +18719,23 @@
         <v>71</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>336</v>
+        <v>265</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>603</v>
+        <v>620</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O161" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="O161" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P161" t="s" s="2">
         <v>71</v>
       </c>
@@ -18786,13 +18759,13 @@
         <v>71</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>71</v>
+        <v>624</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>71</v>
+        <v>625</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>71</v>
@@ -18810,7 +18783,7 @@
         <v>71</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>72</v>
@@ -18827,10 +18800,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18850,21 +18823,23 @@
         <v>71</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>93</v>
+        <v>627</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O162" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="P162" t="s" s="2">
         <v>71</v>
       </c>
@@ -18912,7 +18887,7 @@
         <v>71</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>611</v>
+        <v>626</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>72</v>
@@ -18929,10 +18904,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18946,7 +18921,7 @@
         <v>73</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>71</v>
@@ -18955,19 +18930,17 @@
         <v>71</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>613</v>
+        <v>523</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>614</v>
+        <v>524</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>71</v>
@@ -19016,7 +18989,7 @@
         <v>71</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>72</v>
@@ -19028,15 +19001,15 @@
         <v>90</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>91</v>
+        <v>634</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19059,16 +19032,20 @@
         <v>71</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>93</v>
+        <v>636</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>94</v>
+        <v>571</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>637</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>71</v>
       </c>
@@ -19116,7 +19093,7 @@
         <v>71</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>96</v>
+        <v>635</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>72</v>
@@ -19125,22 +19102,22 @@
         <v>78</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -19150,7 +19127,7 @@
         <v>73</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>71</v>
@@ -19159,18 +19136,20 @@
         <v>71</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>99</v>
+        <v>639</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>100</v>
+        <v>640</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>101</v>
+        <v>641</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O165" s="2"/>
+        <v>642</v>
+      </c>
+      <c r="O165" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="P165" t="s" s="2">
         <v>71</v>
       </c>
@@ -19206,19 +19185,19 @@
         <v>71</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="AC165" t="s" s="2">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="AD165" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>106</v>
+        <v>638</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>72</v>
@@ -19230,633 +19209,11 @@
         <v>90</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="166" hidden="true">
-      <c r="A166" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C166" s="2"/>
-      <c r="D166" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="E166" s="2"/>
-      <c r="F166" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G166" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I166" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J166" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K166" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L166" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="P166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q166" s="2"/>
-      <c r="R166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AG166" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH166" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI166" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="167" hidden="true">
-      <c r="A167" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="C167" s="2"/>
-      <c r="D167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E167" s="2"/>
-      <c r="F167" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G167" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K167" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L167" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="P167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q167" s="2"/>
-      <c r="R167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X167" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="Y167" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="Z167" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AA167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AG167" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH167" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI167" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ167" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="168" hidden="true">
-      <c r="A168" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C168" s="2"/>
-      <c r="D168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E168" s="2"/>
-      <c r="F168" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G168" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K168" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="P168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q168" s="2"/>
-      <c r="R168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AG168" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH168" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI168" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ168" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="169" hidden="true">
-      <c r="A169" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C169" s="2"/>
-      <c r="D169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E169" s="2"/>
-      <c r="F169" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G169" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K169" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="L169" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N169" s="2"/>
-      <c r="O169" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="P169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q169" s="2"/>
-      <c r="R169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ169" t="s" s="2">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="170" hidden="true">
-      <c r="A170" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C170" s="2"/>
-      <c r="D170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E170" s="2"/>
-      <c r="F170" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G170" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K170" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="L170" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="P170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q170" s="2"/>
-      <c r="R170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ170" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="171" hidden="true">
-      <c r="A171" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C171" s="2"/>
-      <c r="D171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E171" s="2"/>
-      <c r="F171" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G171" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K171" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="L171" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="P171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q171" s="2"/>
-      <c r="R171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE171" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF171" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AG171" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ171" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ171">
+  <autoFilter ref="A1:AJ165">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19866,7 +19223,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI170">
+  <conditionalFormatting sqref="A2:AI164">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1115,14 +1115,13 @@
     <t>Organization.active</t>
   </si>
   <si>
-    <t>Whether the organization's record is still in active use</t>
+    <t>isActive</t>
   </si>
   <si>
     <t>Whether the organization's record is still in active use.</t>
   </si>
   <si>
-    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
-This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+    <t>true par défaut; false pour les structures supprimées</t>
   </si>
   <si>
     <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
@@ -1484,28 +1483,28 @@
     <t>Organization.name</t>
   </si>
   <si>
+    <t>raisonSociale</t>
+  </si>
+  <si>
+    <t>A name associated with the organization.</t>
+  </si>
+  <si>
     <t>Raison Sociale de la structure</t>
   </si>
   <si>
-    <t>A name associated with the organization.</t>
-  </si>
-  <si>
-    <t>If the name of an organization changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
-  </si>
-  <si>
     <t>Need to use the name as the label of the organization.</t>
   </si>
   <si>
     <t>Organization.alias</t>
   </si>
   <si>
+    <t>complementRaisonSociale</t>
+  </si>
+  <si>
+    <t>A list of alternate names that the organization is known as, or was known as in the past.</t>
+  </si>
+  <si>
     <t>Enseigne commerciale de la structure</t>
-  </si>
-  <si>
-    <t>A list of alternate names that the organization is known as, or was known as in the past.</t>
-  </si>
-  <si>
-    <t>There are no dates associated with the alias/historic names, as this is not intended to track when names were used, but to assist in searching so that older names can still result in identifying the organization.</t>
   </si>
   <si>
     <t>Over time locations and organizations go through many changes and can be known by different names.
@@ -11193,7 +11192,7 @@
         <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>79</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5066" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5066" uniqueCount="608">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1164,6 +1164,13 @@
   </si>
   <si>
     <t>organizationType</t>
+  </si>
+  <si>
+    <t>Type de strcuture</t>
+  </si>
+  <si>
+    <t>Entitité Juridique : LEGAL-ENTITY; 
+Entité Géographique : GEOGRAPHICAL-ENTITY</t>
   </si>
   <si>
     <t>http://interopsante.org/fhir/ValueSet/fr-organization-type</t>
@@ -11298,7 +11305,7 @@
         <v>73</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>71</v>
@@ -11414,13 +11421,13 @@
         <v>224</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="M91" t="s" s="2">
         <v>359</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>361</v>
@@ -11454,7 +11461,7 @@
         <v>363</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>71</v>
@@ -11489,10 +11496,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11589,10 +11596,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11691,10 +11698,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11717,19 +11724,19 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>71</v>
@@ -11778,7 +11785,7 @@
         <v>71</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>72</v>
@@ -11795,10 +11802,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11895,10 +11902,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11997,10 +12004,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12026,29 +12033,29 @@
         <v>93</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>71</v>
@@ -12084,7 +12091,7 @@
         <v>71</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>72</v>
@@ -12101,10 +12108,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12130,13 +12137,13 @@
         <v>146</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12186,7 +12193,7 @@
         <v>71</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>72</v>
@@ -12203,10 +12210,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12232,16 +12239,16 @@
         <v>99</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>71</v>
@@ -12290,7 +12297,7 @@
         <v>71</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>72</v>
@@ -12307,10 +12314,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12336,16 +12343,16 @@
         <v>146</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>71</v>
@@ -12394,7 +12401,7 @@
         <v>71</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>72</v>
@@ -12411,10 +12418,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12440,16 +12447,16 @@
         <v>269</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>71</v>
@@ -12498,7 +12505,7 @@
         <v>71</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>72</v>
@@ -12515,10 +12522,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12544,16 +12551,16 @@
         <v>146</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>71</v>
@@ -12602,7 +12609,7 @@
         <v>71</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>72</v>
@@ -12619,13 +12626,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>71</v>
@@ -12687,10 +12694,10 @@
         <v>228</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>71</v>
@@ -12725,10 +12732,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12825,10 +12832,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12927,10 +12934,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12953,19 +12960,19 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>71</v>
@@ -13014,7 +13021,7 @@
         <v>71</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>72</v>
@@ -13031,10 +13038,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13131,10 +13138,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13233,10 +13240,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13262,29 +13269,29 @@
         <v>93</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>71</v>
@@ -13320,7 +13327,7 @@
         <v>71</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>72</v>
@@ -13337,10 +13344,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13366,13 +13373,13 @@
         <v>146</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13422,7 +13429,7 @@
         <v>71</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>72</v>
@@ -13439,10 +13446,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13468,16 +13475,16 @@
         <v>99</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>71</v>
@@ -13526,7 +13533,7 @@
         <v>71</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>72</v>
@@ -13543,10 +13550,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13572,16 +13579,16 @@
         <v>146</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>71</v>
@@ -13630,7 +13637,7 @@
         <v>71</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>72</v>
@@ -13647,10 +13654,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13676,16 +13683,16 @@
         <v>269</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>71</v>
@@ -13734,7 +13741,7 @@
         <v>71</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>72</v>
@@ -13751,10 +13758,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13780,16 +13787,16 @@
         <v>146</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>71</v>
@@ -13838,7 +13845,7 @@
         <v>71</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>72</v>
@@ -13855,13 +13862,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>71</v>
@@ -13923,10 +13930,10 @@
         <v>228</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>71</v>
@@ -13961,10 +13968,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14061,10 +14068,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14163,10 +14170,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14189,19 +14196,19 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>71</v>
@@ -14250,7 +14257,7 @@
         <v>71</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>72</v>
@@ -14267,10 +14274,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14367,10 +14374,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14469,10 +14476,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14498,23 +14505,23 @@
         <v>93</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>71</v>
@@ -14556,7 +14563,7 @@
         <v>71</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>72</v>
@@ -14573,10 +14580,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14602,13 +14609,13 @@
         <v>146</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14658,7 +14665,7 @@
         <v>71</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>72</v>
@@ -14675,10 +14682,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14704,16 +14711,16 @@
         <v>99</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>71</v>
@@ -14762,7 +14769,7 @@
         <v>71</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>72</v>
@@ -14779,10 +14786,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14808,16 +14815,16 @@
         <v>146</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>71</v>
@@ -14866,7 +14873,7 @@
         <v>71</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>72</v>
@@ -14883,10 +14890,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14912,16 +14919,16 @@
         <v>269</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>71</v>
@@ -14970,7 +14977,7 @@
         <v>71</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>72</v>
@@ -14987,10 +14994,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15016,16 +15023,16 @@
         <v>146</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>71</v>
@@ -15074,7 +15081,7 @@
         <v>71</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>72</v>
@@ -15091,13 +15098,13 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>71</v>
@@ -15110,7 +15117,7 @@
         <v>73</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>71</v>
@@ -15122,7 +15129,7 @@
         <v>224</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>359</v>
@@ -15160,7 +15167,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>71</v>
@@ -15195,13 +15202,13 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>71</v>
@@ -15214,7 +15221,7 @@
         <v>73</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>71</v>
@@ -15226,7 +15233,7 @@
         <v>224</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M128" t="s" s="2">
         <v>359</v>
@@ -15264,7 +15271,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>71</v>
@@ -15299,13 +15306,13 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>71</v>
@@ -15318,7 +15325,7 @@
         <v>73</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>71</v>
@@ -15330,7 +15337,7 @@
         <v>224</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M129" t="s" s="2">
         <v>359</v>
@@ -15368,7 +15375,7 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>71</v>
@@ -15403,10 +15410,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15432,16 +15439,16 @@
         <v>146</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>71</v>
@@ -15490,7 +15497,7 @@
         <v>71</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>72</v>
@@ -15507,10 +15514,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15536,16 +15543,16 @@
         <v>146</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>71</v>
@@ -15594,7 +15601,7 @@
         <v>71</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>72</v>
@@ -15611,10 +15618,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15637,19 +15644,19 @@
         <v>71</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>71</v>
@@ -15698,7 +15705,7 @@
         <v>71</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>72</v>
@@ -15707,18 +15714,18 @@
         <v>73</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15815,10 +15822,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15917,13 +15924,13 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>122</v>
@@ -15945,10 +15952,10 @@
         <v>71</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M135" t="s" s="2">
         <v>136</v>
@@ -16021,10 +16028,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16050,13 +16057,13 @@
         <v>99</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -16085,10 +16092,10 @@
         <v>228</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>71</v>
@@ -16106,7 +16113,7 @@
         <v>71</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>72</v>
@@ -16115,7 +16122,7 @@
         <v>78</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>91</v>
@@ -16123,10 +16130,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16152,16 +16159,16 @@
         <v>146</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>71</v>
@@ -16210,7 +16217,7 @@
         <v>71</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>72</v>
@@ -16227,10 +16234,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16256,16 +16263,16 @@
         <v>99</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>71</v>
@@ -16293,10 +16300,10 @@
         <v>228</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>71</v>
@@ -16314,7 +16321,7 @@
         <v>71</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>72</v>
@@ -16331,10 +16338,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16357,16 +16364,16 @@
         <v>79</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -16416,7 +16423,7 @@
         <v>71</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>72</v>
@@ -16433,10 +16440,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16462,13 +16469,13 @@
         <v>163</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -16518,7 +16525,7 @@
         <v>71</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>72</v>
@@ -16535,10 +16542,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16561,19 +16568,19 @@
         <v>71</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>71</v>
@@ -16622,7 +16629,7 @@
         <v>71</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>72</v>
@@ -16634,15 +16641,15 @@
         <v>90</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16665,19 +16672,19 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>71</v>
@@ -16726,7 +16733,7 @@
         <v>71</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>72</v>
@@ -16743,10 +16750,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16843,10 +16850,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16945,10 +16952,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16974,13 +16981,13 @@
         <v>146</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -17030,7 +17037,7 @@
         <v>71</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>72</v>
@@ -17039,7 +17046,7 @@
         <v>78</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>91</v>
@@ -17047,10 +17054,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17076,13 +17083,13 @@
         <v>93</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -17111,10 +17118,10 @@
         <v>321</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>71</v>
@@ -17132,7 +17139,7 @@
         <v>71</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>72</v>
@@ -17149,10 +17156,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17178,13 +17185,13 @@
         <v>299</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -17234,7 +17241,7 @@
         <v>71</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>72</v>
@@ -17251,10 +17258,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17280,13 +17287,13 @@
         <v>146</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -17336,7 +17343,7 @@
         <v>71</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>72</v>
@@ -17353,10 +17360,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17379,19 +17386,19 @@
         <v>71</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>71</v>
@@ -17440,7 +17447,7 @@
         <v>71</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>72</v>
@@ -17457,10 +17464,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17557,10 +17564,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17659,14 +17666,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -17688,10 +17695,10 @@
         <v>123</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>126</v>
@@ -17746,7 +17753,7 @@
         <v>71</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>72</v>
@@ -17763,10 +17770,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17792,16 +17799,16 @@
         <v>224</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>71</v>
@@ -17829,10 +17836,10 @@
         <v>321</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>71</v>
@@ -17850,7 +17857,7 @@
         <v>71</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>72</v>
@@ -17867,10 +17874,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17893,19 +17900,19 @@
         <v>71</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>71</v>
@@ -17954,7 +17961,7 @@
         <v>71</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>72</v>
@@ -17971,10 +17978,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17997,17 +18004,17 @@
         <v>71</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>71</v>
@@ -18056,7 +18063,7 @@
         <v>71</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>72</v>
@@ -18068,15 +18075,15 @@
         <v>90</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18099,19 +18106,19 @@
         <v>71</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>71</v>
@@ -18160,7 +18167,7 @@
         <v>71</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>72</v>
@@ -18177,10 +18184,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18203,19 +18210,19 @@
         <v>71</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>71</v>
@@ -18264,7 +18271,7 @@
         <v>71</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>72</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -18201,7 +18201,7 @@
         <v>73</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>71</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4931,7 +4931,7 @@
         <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>71</v>
@@ -5435,7 +5435,7 @@
         <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>71</v>
@@ -6039,7 +6039,7 @@
         <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>71</v>
@@ -6543,7 +6543,7 @@
         <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>71</v>
@@ -7047,7 +7047,7 @@
         <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>71</v>
@@ -7651,7 +7651,7 @@
         <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>71</v>
@@ -8255,7 +8255,7 @@
         <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>71</v>
@@ -8861,7 +8861,7 @@
         <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>71</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4916" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4916" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -611,30 +611,36 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>Organization.extension:organization-digitalCertificate</t>
-  </si>
-  <si>
-    <t>organization-digitalCertificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/digitalCertificate}
+    <t>Organization.extension:as-ext-digital-certificate</t>
+  </si>
+  <si>
+    <t>as-ext-digital-certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-digital-certificate}
 </t>
   </si>
   <si>
     <t>[DR] : certificat</t>
   </si>
   <si>
-    <t>Organization.extension:organization-pharmacyLicence</t>
-  </si>
-  <si>
-    <t>organization-pharmacyLicence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/organization-pharmacyLicence}
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les certificats utilisés par les professionnels et les structures comme moyen d'identification.</t>
+  </si>
+  <si>
+    <t>Organization.extension:as-ext-organization-pharmacy-licence</t>
+  </si>
+  <si>
+    <t>as-ext-organization-pharmacy-licence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-organization-pharmacy-licence}
 </t>
   </si>
   <si>
     <t>numeroLicence</t>
+  </si>
+  <si>
+    <t>Numéro de la licence d'exploitation d’une officine.</t>
   </si>
   <si>
     <t>Organization.modifierExtension</t>
@@ -1629,7 +1635,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-mailbox-mss-metadata}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-mailbox-mss-metadata}
 </t>
   </si>
   <si>
@@ -1708,6 +1714,9 @@
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
   </si>
   <si>
+    <t>Description fonctionnelle de la boîte aux lettres</t>
+  </si>
+  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
   </si>
   <si>
@@ -1718,9 +1727,6 @@
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.value[x]</t>
-  </si>
-  <si>
-    <t>Description fonctionnelle de la boîte aux lettres</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible</t>
@@ -1836,7 +1842,7 @@
     <t>Organization.contact.telecom.extension.url</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-mailbox-mss-metadata</t>
+    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-mailbox-mss-metadata</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
@@ -2234,7 +2240,7 @@
   <cols>
     <col min="1" max="1" width="118.80859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="56.87890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="29.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="35.7890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3617,7 +3623,7 @@
         <v>72</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>71</v>
@@ -3818,7 +3824,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>78</v>
@@ -4449,7 +4455,7 @@
         <v>193</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4517,13 +4523,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>71</v>
@@ -4545,13 +4551,13 @@
         <v>71</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4619,10 +4625,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4648,16 +4654,16 @@
         <v>123</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>71</v>
@@ -4706,7 +4712,7 @@
         <v>129</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>72</v>
@@ -4723,10 +4729,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4749,19 +4755,19 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>71</v>
@@ -4810,7 +4816,7 @@
         <v>71</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>72</v>
@@ -4819,7 +4825,7 @@
         <v>73</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>91</v>
@@ -4827,10 +4833,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4927,10 +4933,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5029,10 +5035,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5058,23 +5064,23 @@
         <v>99</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>71</v>
@@ -5092,13 +5098,13 @@
         <v>71</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>71</v>
@@ -5116,7 +5122,7 @@
         <v>71</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>72</v>
@@ -5133,10 +5139,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5159,19 +5165,19 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>71</v>
@@ -5196,13 +5202,13 @@
         <v>71</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>71</v>
@@ -5220,7 +5226,7 @@
         <v>71</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>72</v>
@@ -5237,10 +5243,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5266,16 +5272,16 @@
         <v>93</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>71</v>
@@ -5288,7 +5294,7 @@
         <v>71</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>71</v>
@@ -5324,7 +5330,7 @@
         <v>71</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>72</v>
@@ -5341,10 +5347,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5370,13 +5376,13 @@
         <v>146</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5390,7 +5396,7 @@
         <v>71</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>71</v>
@@ -5426,7 +5432,7 @@
         <v>71</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>72</v>
@@ -5443,10 +5449,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5472,13 +5478,13 @@
         <v>163</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5528,7 +5534,7 @@
         <v>71</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>72</v>
@@ -5540,15 +5546,15 @@
         <v>90</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5571,16 +5577,16 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5630,7 +5636,7 @@
         <v>71</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>72</v>
@@ -5642,15 +5648,15 @@
         <v>90</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5673,70 +5679,70 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q34" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="R34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="P34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q34" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="R34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>72</v>
@@ -5753,10 +5759,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5779,19 +5785,19 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>71</v>
@@ -5816,19 +5822,19 @@
         <v>71</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -5838,7 +5844,7 @@
         <v>129</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>72</v>
@@ -5855,13 +5861,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>71</v>
@@ -5883,19 +5889,19 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>71</v>
@@ -5920,13 +5926,13 @@
         <v>71</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>71</v>
@@ -5944,7 +5950,7 @@
         <v>71</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>72</v>
@@ -5961,10 +5967,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6061,10 +6067,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6163,10 +6169,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6189,19 +6195,19 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>71</v>
@@ -6250,7 +6256,7 @@
         <v>71</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>72</v>
@@ -6267,10 +6273,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6367,10 +6373,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6469,10 +6475,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6498,29 +6504,29 @@
         <v>93</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>71</v>
@@ -6556,7 +6562,7 @@
         <v>71</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>72</v>
@@ -6573,10 +6579,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6602,13 +6608,13 @@
         <v>146</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6658,7 +6664,7 @@
         <v>71</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>72</v>
@@ -6675,10 +6681,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6704,16 +6710,16 @@
         <v>99</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>71</v>
@@ -6762,7 +6768,7 @@
         <v>71</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>72</v>
@@ -6779,10 +6785,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6808,16 +6814,16 @@
         <v>146</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>71</v>
@@ -6866,7 +6872,7 @@
         <v>71</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>72</v>
@@ -6883,10 +6889,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6909,19 +6915,19 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>71</v>
@@ -6970,7 +6976,7 @@
         <v>71</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>72</v>
@@ -6987,10 +6993,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7016,16 +7022,16 @@
         <v>146</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>71</v>
@@ -7074,7 +7080,7 @@
         <v>71</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>72</v>
@@ -7091,13 +7097,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>71</v>
@@ -7119,19 +7125,19 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>71</v>
@@ -7156,13 +7162,13 @@
         <v>71</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>71</v>
@@ -7180,7 +7186,7 @@
         <v>71</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>72</v>
@@ -7197,10 +7203,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7297,10 +7303,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7399,10 +7405,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7425,19 +7431,19 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>71</v>
@@ -7486,7 +7492,7 @@
         <v>71</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>72</v>
@@ -7503,10 +7509,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7603,10 +7609,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7705,10 +7711,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7734,29 +7740,29 @@
         <v>93</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>71</v>
@@ -7792,7 +7798,7 @@
         <v>71</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>72</v>
@@ -7809,10 +7815,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7838,13 +7844,13 @@
         <v>146</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7894,7 +7900,7 @@
         <v>71</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>72</v>
@@ -7911,10 +7917,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7940,16 +7946,16 @@
         <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>71</v>
@@ -7998,7 +8004,7 @@
         <v>71</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>72</v>
@@ -8015,10 +8021,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8044,16 +8050,16 @@
         <v>146</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>71</v>
@@ -8102,7 +8108,7 @@
         <v>71</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>72</v>
@@ -8119,10 +8125,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8145,19 +8151,19 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>71</v>
@@ -8206,7 +8212,7 @@
         <v>71</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>72</v>
@@ -8223,10 +8229,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8252,16 +8258,16 @@
         <v>146</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>71</v>
@@ -8310,7 +8316,7 @@
         <v>71</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>72</v>
@@ -8327,13 +8333,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>71</v>
@@ -8355,19 +8361,19 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>71</v>
@@ -8392,13 +8398,13 @@
         <v>71</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>71</v>
@@ -8416,7 +8422,7 @@
         <v>71</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>72</v>
@@ -8433,10 +8439,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8533,10 +8539,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8635,10 +8641,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8661,19 +8667,19 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>71</v>
@@ -8722,7 +8728,7 @@
         <v>71</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>72</v>
@@ -8739,10 +8745,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8839,10 +8845,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8941,10 +8947,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8970,23 +8976,23 @@
         <v>93</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>71</v>
@@ -9028,7 +9034,7 @@
         <v>71</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>72</v>
@@ -9045,10 +9051,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9074,13 +9080,13 @@
         <v>146</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9130,7 +9136,7 @@
         <v>71</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>72</v>
@@ -9147,10 +9153,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9176,16 +9182,16 @@
         <v>99</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>71</v>
@@ -9234,7 +9240,7 @@
         <v>71</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>72</v>
@@ -9251,10 +9257,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9280,16 +9286,16 @@
         <v>146</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>71</v>
@@ -9338,7 +9344,7 @@
         <v>71</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>72</v>
@@ -9355,10 +9361,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9381,19 +9387,19 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>71</v>
@@ -9442,7 +9448,7 @@
         <v>71</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>72</v>
@@ -9459,10 +9465,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9488,16 +9494,16 @@
         <v>146</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>71</v>
@@ -9546,7 +9552,7 @@
         <v>71</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>72</v>
@@ -9563,13 +9569,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>71</v>
@@ -9591,19 +9597,19 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>71</v>
@@ -9628,11 +9634,11 @@
         <v>71</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>71</v>
@@ -9650,7 +9656,7 @@
         <v>71</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>72</v>
@@ -9667,13 +9673,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>71</v>
@@ -9695,19 +9701,19 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>71</v>
@@ -9732,11 +9738,11 @@
         <v>71</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>71</v>
@@ -9754,7 +9760,7 @@
         <v>71</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>72</v>
@@ -9771,13 +9777,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>71</v>
@@ -9799,19 +9805,19 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>71</v>
@@ -9836,11 +9842,11 @@
         <v>71</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>71</v>
@@ -9858,7 +9864,7 @@
         <v>71</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>72</v>
@@ -9875,10 +9881,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9904,16 +9910,16 @@
         <v>146</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>71</v>
@@ -9962,7 +9968,7 @@
         <v>71</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>72</v>
@@ -9971,7 +9977,7 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>91</v>
@@ -9979,10 +9985,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10008,16 +10014,16 @@
         <v>146</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>71</v>
@@ -10066,7 +10072,7 @@
         <v>71</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>72</v>
@@ -10083,10 +10089,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10109,19 +10115,19 @@
         <v>71</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>71</v>
@@ -10170,7 +10176,7 @@
         <v>71</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>72</v>
@@ -10179,18 +10185,18 @@
         <v>73</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10287,10 +10293,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10389,13 +10395,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>122</v>
@@ -10417,10 +10423,10 @@
         <v>71</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>136</v>
@@ -10493,10 +10499,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10522,13 +10528,13 @@
         <v>99</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10554,13 +10560,13 @@
         <v>71</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>71</v>
@@ -10578,7 +10584,7 @@
         <v>71</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>72</v>
@@ -10587,7 +10593,7 @@
         <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>91</v>
@@ -10595,10 +10601,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10624,16 +10630,16 @@
         <v>146</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>71</v>
@@ -10682,7 +10688,7 @@
         <v>71</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>72</v>
@@ -10699,10 +10705,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10728,16 +10734,16 @@
         <v>99</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>71</v>
@@ -10762,13 +10768,13 @@
         <v>71</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>71</v>
@@ -10786,7 +10792,7 @@
         <v>71</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>72</v>
@@ -10803,10 +10809,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10829,16 +10835,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10888,7 +10894,7 @@
         <v>71</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>72</v>
@@ -10905,10 +10911,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10934,13 +10940,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10990,7 +10996,7 @@
         <v>71</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>72</v>
@@ -11002,15 +11008,15 @@
         <v>90</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11033,19 +11039,19 @@
         <v>71</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>71</v>
@@ -11094,7 +11100,7 @@
         <v>71</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>72</v>
@@ -11106,15 +11112,15 @@
         <v>90</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11137,19 +11143,19 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>71</v>
@@ -11198,7 +11204,7 @@
         <v>71</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>72</v>
@@ -11210,15 +11216,15 @@
         <v>90</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11315,10 +11321,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11417,10 +11423,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11446,13 +11452,13 @@
         <v>146</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11502,7 +11508,7 @@
         <v>71</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>72</v>
@@ -11511,7 +11517,7 @@
         <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>91</v>
@@ -11519,10 +11525,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11548,13 +11554,13 @@
         <v>93</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11580,13 +11586,13 @@
         <v>71</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>71</v>
@@ -11604,7 +11610,7 @@
         <v>71</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>72</v>
@@ -11621,10 +11627,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11647,16 +11653,16 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11706,7 +11712,7 @@
         <v>71</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>72</v>
@@ -11723,10 +11729,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11752,13 +11758,13 @@
         <v>146</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11808,7 +11814,7 @@
         <v>71</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>72</v>
@@ -11825,10 +11831,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11851,19 +11857,19 @@
         <v>71</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>71</v>
@@ -11912,7 +11918,7 @@
         <v>71</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>72</v>
@@ -11929,10 +11935,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12029,10 +12035,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12131,14 +12137,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12160,16 +12166,16 @@
         <v>123</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>71</v>
@@ -12218,7 +12224,7 @@
         <v>71</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>72</v>
@@ -12235,10 +12241,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12261,19 +12267,19 @@
         <v>71</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>71</v>
@@ -12298,13 +12304,13 @@
         <v>71</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>71</v>
@@ -12322,7 +12328,7 @@
         <v>71</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>72</v>
@@ -12339,10 +12345,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12365,19 +12371,19 @@
         <v>71</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>71</v>
@@ -12426,7 +12432,7 @@
         <v>71</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>72</v>
@@ -12443,10 +12449,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12469,17 +12475,17 @@
         <v>71</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>71</v>
@@ -12516,7 +12522,7 @@
         <v>71</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AC100" s="2"/>
       <c r="AD100" t="s" s="2">
@@ -12526,7 +12532,7 @@
         <v>129</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>72</v>
@@ -12538,18 +12544,18 @@
         <v>90</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>71</v>
@@ -12571,17 +12577,17 @@
         <v>71</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>71</v>
@@ -12630,7 +12636,7 @@
         <v>71</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>72</v>
@@ -12647,10 +12653,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12747,10 +12753,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12849,13 +12855,13 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>122</v>
@@ -12877,10 +12883,10 @@
         <v>71</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>136</v>
@@ -12953,13 +12959,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="B105" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="C105" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>71</v>
@@ -12981,13 +12987,13 @@
         <v>71</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13055,10 +13061,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13155,10 +13161,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13257,13 +13263,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>71</v>
@@ -13288,10 +13294,10 @@
         <v>123</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -13359,10 +13365,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13459,10 +13465,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13488,10 +13494,10 @@
         <v>123</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13559,10 +13565,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13602,7 +13608,7 @@
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>71</v>
@@ -13661,10 +13667,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13687,7 +13693,7 @@
         <v>71</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>164</v>
@@ -13759,13 +13765,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>71</v>
@@ -13787,7 +13793,7 @@
         <v>71</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>164</v>
@@ -13820,13 +13826,13 @@
         <v>71</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>71</v>
@@ -13861,10 +13867,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>138</v>
@@ -13892,10 +13898,10 @@
         <v>123</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13963,10 +13969,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14063,10 +14069,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14092,10 +14098,10 @@
         <v>123</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14163,10 +14169,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14265,10 +14271,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14294,7 +14300,7 @@
         <v>146</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>545</v>
+        <v>164</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>165</v>
@@ -14365,13 +14371,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>71</v>
@@ -14396,10 +14402,10 @@
         <v>123</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14467,10 +14473,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14567,10 +14573,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14596,10 +14602,10 @@
         <v>123</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14667,10 +14673,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14710,7 +14716,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>71</v>
@@ -14769,10 +14775,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14869,13 +14875,13 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>71</v>
@@ -14900,10 +14906,10 @@
         <v>123</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14971,10 +14977,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15071,10 +15077,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15100,10 +15106,10 @@
         <v>123</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15171,10 +15177,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15214,7 +15220,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>71</v>
@@ -15273,10 +15279,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15373,13 +15379,13 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>71</v>
@@ -15404,10 +15410,10 @@
         <v>123</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -15475,10 +15481,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15575,10 +15581,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15604,10 +15610,10 @@
         <v>123</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -15675,10 +15681,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15718,7 +15724,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>71</v>
@@ -15777,10 +15783,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15877,13 +15883,13 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>71</v>
@@ -15908,10 +15914,10 @@
         <v>123</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15979,10 +15985,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16079,10 +16085,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16108,10 +16114,10 @@
         <v>123</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -16179,10 +16185,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16222,7 +16228,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>71</v>
@@ -16281,10 +16287,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16307,7 +16313,7 @@
         <v>71</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>164</v>
@@ -16381,13 +16387,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>71</v>
@@ -16412,10 +16418,10 @@
         <v>123</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -16483,10 +16489,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16583,10 +16589,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16612,10 +16618,10 @@
         <v>123</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -16683,10 +16689,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16726,7 +16732,7 @@
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="S142" t="s" s="2">
         <v>71</v>
@@ -16785,10 +16791,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16811,7 +16817,7 @@
         <v>71</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L143" t="s" s="2">
         <v>164</v>
@@ -16885,10 +16891,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16928,7 +16934,7 @@
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>71</v>
@@ -16987,10 +16993,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17013,7 +17019,7 @@
         <v>71</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L145" t="s" s="2">
         <v>164</v>
@@ -17087,10 +17093,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17116,13 +17122,13 @@
         <v>99</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -17133,7 +17139,7 @@
         <v>71</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>71</v>
@@ -17148,13 +17154,13 @@
         <v>71</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>71</v>
@@ -17172,7 +17178,7 @@
         <v>71</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>72</v>
@@ -17181,7 +17187,7 @@
         <v>78</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>91</v>
@@ -17189,10 +17195,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17218,16 +17224,16 @@
         <v>146</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>71</v>
@@ -17276,7 +17282,7 @@
         <v>71</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>72</v>
@@ -17293,10 +17299,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17322,16 +17328,16 @@
         <v>99</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>71</v>
@@ -17356,13 +17362,13 @@
         <v>71</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>71</v>
@@ -17380,7 +17386,7 @@
         <v>71</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>72</v>
@@ -17397,10 +17403,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17423,16 +17429,16 @@
         <v>79</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -17482,7 +17488,7 @@
         <v>71</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>72</v>
@@ -17499,10 +17505,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17528,13 +17534,13 @@
         <v>163</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -17584,7 +17590,7 @@
         <v>71</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>72</v>
@@ -17596,15 +17602,15 @@
         <v>90</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17627,19 +17633,19 @@
         <v>71</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>71</v>
@@ -17688,7 +17694,7 @@
         <v>71</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>72</v>
@@ -17705,10 +17711,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17731,19 +17737,19 @@
         <v>71</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>71</v>
@@ -17792,7 +17798,7 @@
         <v>71</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>72</v>
@@ -17804,7 +17810,7 @@
         <v>90</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
